--- a/artfynd/A 2344-2024 artfynd.xlsx
+++ b/artfynd/A 2344-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2344-2024 artfynd.xlsx
+++ b/artfynd/A 2344-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110045291</v>
+        <v>110045292</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>848076.4715823013</v>
+        <v>847811</v>
       </c>
       <c r="R2" t="n">
-        <v>7391829.4720112</v>
+        <v>7392162</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110045287</v>
+        <v>110045312</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>847901.1650536681</v>
+        <v>847883</v>
       </c>
       <c r="R3" t="n">
-        <v>7391869.993568911</v>
+        <v>7392056</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +862,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110045292</v>
+        <v>110045332</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>847811.0541601016</v>
+        <v>847919</v>
       </c>
       <c r="R4" t="n">
-        <v>7392161.920072145</v>
+        <v>7392034</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110045273</v>
+        <v>128796337</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rudjärvsberget utvidgning, Nb</t>
+          <t>Rudjärvberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>847942.2642887081</v>
+        <v>848221</v>
       </c>
       <c r="R5" t="n">
-        <v>7391928.878857361</v>
+        <v>7391951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1061,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alexander Singer, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110045312</v>
+        <v>128796455</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1088,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rudjärvsberget utvidgning, Nb</t>
+          <t>Rudjärvberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>847883.4145593077</v>
+        <v>848224</v>
       </c>
       <c r="R6" t="n">
-        <v>7392055.943916244</v>
+        <v>7391947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1142,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,49 +1172,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Alexander Singer, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110045335</v>
+        <v>110045273</v>
       </c>
       <c r="B7" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>847871.2139527975</v>
+        <v>847942</v>
       </c>
       <c r="R7" t="n">
-        <v>7392072.579629145</v>
+        <v>7391929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1256,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,44 +1278,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110045332</v>
+        <v>110045287</v>
       </c>
       <c r="B8" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>847919.6972178321</v>
+        <v>847901</v>
       </c>
       <c r="R8" t="n">
-        <v>7392034.263741128</v>
+        <v>7391870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1353,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,44 +1375,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110045309</v>
+        <v>110045291</v>
       </c>
       <c r="B9" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>847934.7210093382</v>
+        <v>848076</v>
       </c>
       <c r="R9" t="n">
-        <v>7391969.524012534</v>
+        <v>7391829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1450,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,22 +1472,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110045336</v>
+        <v>110045324</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1490,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>848070.71000637</v>
+        <v>847876</v>
       </c>
       <c r="R10" t="n">
-        <v>7391817.438318526</v>
+        <v>7391850</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1547,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,10 +1569,814 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110045333</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rudjärvsberget utvidgning, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>847983</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7391783</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
           <t>Frédéric Forsmark</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110045336</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rudjärvsberget utvidgning, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>848070</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7391817</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110045335</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rudjärvsberget utvidgning, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>847871</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7392073</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110045309</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57774</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rudjärvsberget utvidgning, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>847934</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7391969</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110045337</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rudjärvsberget utvidgning, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>848227</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7391970</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128796353</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rudjärvberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>848225</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7391970</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128796426</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Rudjärvberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>848202</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7391995</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer, Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>110045299</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rudjärvsberget utvidgning, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>848048</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7391871</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2344-2024 artfynd.xlsx
+++ b/artfynd/A 2344-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045292</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045332</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
           <t>Boreala Svampskogar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128796337</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
           <t>Boreala Svampskogar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128796455</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045273</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045287</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045291</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045324</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045333</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045336</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045335</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045309</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045337</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2169,6 +2244,11 @@
           <t>Boreala Svampskogar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128796353</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2280,6 +2360,11 @@
           <t>Boreala Svampskogar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128796426</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,8 +2462,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045299</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>